--- a/www/download/COUNTRY.KOR.rpO1.xlsx
+++ b/www/download/COUNTRY.KOR.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>Coreia do Sul</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>769.230769191585</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>806.451604195844</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>934.579434669612</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1388.88887012112</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>1190.47621025982</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>1136.36362231776</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1298.70133322324</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1250.00002742103</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>1190.47619916019</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1149.42530127868</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>1020.40814942861</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>952.380984338174</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>925.925956818682</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>1081.23300950843</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1270.08966179751</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20.398</t>
+          <t>2.64203673908373</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.837</t>
+          <t>2.52169525034348</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.201</t>
+          <t>2.49893069174484</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.918</t>
+          <t>2.51144980478821</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20.277</t>
+          <t>2.64749110820945</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.136</t>
+          <t>2.59274472219153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.557</t>
+          <t>2.4557305886614</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.152</t>
+          <t>2.52037043052123</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22.117</t>
+          <t>2.62966235479577</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22.534</t>
+          <t>2.53043799191937</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>2.53603429180441</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>23.133</t>
+          <t>2.46713774429211</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>23.418</t>
+          <t>2.39088931088908</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>23.561</t>
+          <t>2.30472065255997</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>2.23910923298113</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12.899</t>
+          <t>3.98546138956809</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>3.88844735477574</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.405</t>
+          <t>3.73770162008812</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12.296</t>
+          <t>3.75964369191345</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12.663</t>
+          <t>3.94938310938552</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.361</t>
+          <t>3.81649901724485</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13.659</t>
+          <t>3.81526874149158</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.182</t>
+          <t>3.94304972289127</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.403</t>
+          <t>4.07382238524009</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>14.894</t>
+          <t>3.93320636395679</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>15.186</t>
+          <t>4.1261016816263</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15.551</t>
+          <t>4.03152161621974</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>15.97</t>
+          <t>3.92395304896605</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>16.067</t>
+          <t>3.80634540203501</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>16.019</t>
+          <t>3.70885944369883</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>51162.193</t>
+          <t>4.56993883100061</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50854.307</t>
+          <t>4.5633389210653</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51302.684</t>
+          <t>4.44251781670852</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48438.841</t>
+          <t>4.56643677836922</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50338.267</t>
+          <t>4.58211601465838</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>51635.805</t>
+          <t>4.52049761224294</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>52111.252</t>
+          <t>4.71482974825997</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>53200.369</t>
+          <t>4.89702406907653</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>53124.252</t>
+          <t>5.17570606148939</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>55887.331</t>
+          <t>5.11426726659356</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>54220.887</t>
+          <t>5.10921025009616</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>54641.266</t>
+          <t>4.99250717361609</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>53454.996</t>
+          <t>4.86711457192435</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>53781.163</t>
+          <t>4.72780146682525</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>53619.22</t>
+          <t>4.6073613456249</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32640.761</t>
+          <t>37966219051946.4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32366.566</t>
+          <t>37504881967624</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>32542.482</t>
+          <t>35712366303826.6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>29972.52</t>
+          <t>27143874640954.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>31616.61</t>
+          <t>35178333384029</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>32772.416</t>
+          <t>46765126613740.4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33139.63</t>
+          <t>47698517400474.2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34146.109</t>
+          <t>51074387565602.9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>34675.124</t>
+          <t>55190632172356.5</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>37056.547</t>
+          <t>52898856213579.4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>36350.538</t>
+          <t>57831830219335.9</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>36940.81</t>
+          <t>56268820023357.6</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>36652.904</t>
+          <t>46415659253540.6</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>36876.55</t>
+          <t>34062035168890.8</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>36765.509</t>
+          <t>29014081646529.5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>4469643820963.19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>4384898787091.88</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>4125063787827.93</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>2959924823768.49</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>3919078586568.67</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>5070522203823.43</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>5196057697460.35</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>5700366979396.49</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>6213786874190.05</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>5751229075944.86</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>6147675478131.85</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>5976420091802.78</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>4914959557238.82</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>3338471861277.03</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2883069577037.74</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>1127397886.25902</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>1049834527.38652</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>1068358578.64276</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>1174661519.13458</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1210657134.96729</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>1407199572.8535</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>1543047351.98258</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>1480086101.59458</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>1426772025.80542</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1156414162.79501</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>1056748728.17188</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>902778520.952207</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>659442587.189248</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>482767393.228675</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>478323488.681883</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>861460.301026862</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>962105.707341543</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>905200.759965294</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>593928.099946987</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>711535.595040002</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>820081.544451802</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>814349.103583612</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>920275.675863566</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>1053593.91097591</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>1185037.67929723</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>1417806.15148464</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>1579464.32138535</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>1718147.70764043</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>1543252.23997828</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>1404219.06011381</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>1706835.25625428</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>1893836.58051246</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>1765439.26272485</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>1217747.31843259</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>1471105.22034596</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>32.71</t>
+          <t>1724357.48887875</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>1663075.63366519</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>1861853.07513373</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>2113946.97616843</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>2435281.00056449</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>2980216.78017985</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>3363548.40254289</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>3700107.12949776</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>3617655.26627425</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>3208213.19113769</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.59</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>145883.213984109</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>158021.42916051</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>150136.590747949</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>108933.929406134</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>133260.804699939</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>152461.199303685</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>136306.255719661</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>150949.507231172</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>166236.839270636</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>179758.671079501</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>208079.568811872</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>234989.61719292</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>255150.264156843</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>247664.328440945</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>222593.277422626</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>769.230769191585</t>
+          <t>346510.878437335</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>806.451604195844</t>
+          <t>332189.302052415</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>934.579434669612</t>
+          <t>307725.758137108</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1388.88887012112</t>
+          <t>240722.578380651</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1190.47621025982</t>
+          <t>309490.530408961</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1136.36362231776</t>
+          <t>379501.699260791</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1298.70133322324</t>
+          <t>380412.745988751</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1250.00002742103</t>
+          <t>401943.800549745</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1190.47619916019</t>
+          <t>431423.097562317</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1149.42530127868</t>
+          <t>386144.022824282</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1020.40814942861</t>
+          <t>404825.199402861</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>952.380984338174</t>
+          <t>384310.982689395</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>925.925956818682</t>
+          <t>307762.026126413</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1081.23300950843</t>
+          <t>207778.645514457</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1270.08966179751</t>
+          <t>179977.416945782</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>-711073660617.838</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>-913488918518.364</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-846170570815.509</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>-406849426901.559</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>-427242338779.36</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>-832916634824.132</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1188085864438.38</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>-1037040446583.8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>-1154028448359.25</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>-1083605630968.82</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>-1356889551581.14</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1365894082321.06</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>-1139043346223.36</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>-801184390543.431</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>-837587256506.008</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-789707787011.205</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>-927308335154.068</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>-832287514778.827</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>-478034346243.137</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>-410522759876.83</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>-631359913968.039</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-983356406956.418</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>-819739841386.498</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>-951100690475.314</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>-931626143642.363</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>-1180303300239.56</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>-1143224136420.16</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>-959583266523.995</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-578109247121.599</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-709891921775.979</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.761</t>
+          <t>78634126393.3677</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>13819416635.7042</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.816</t>
+          <t>-13883056036.682</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>71184919341.5777</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>-16719578902.5299</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.701</t>
+          <t>-201556720856.093</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>-204729457481.966</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>-217300605197.298</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.104</t>
+          <t>-202927757883.935</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.357</t>
+          <t>-151979487326.453</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.795</t>
+          <t>-176586251341.581</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.142</t>
+          <t>-222669945900.9</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.441</t>
+          <t>-179460079699.366</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.361</t>
+          <t>-223075143421.832</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.066</t>
+          <t>-127695334730.028</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.109</t>
+          <t>1553227.26427254</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1444851.67758563</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.132</t>
+          <t>1303919.70812321</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1014517.65670755</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.995</t>
+          <t>1345395.5166921</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.154</t>
+          <t>1617419.59428112</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1577662.66252919</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1690628.66151626</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1865495.00388884</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1621310.90857783</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.914</t>
+          <t>1711266.17235077</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.185</t>
+          <t>1592031.55405126</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.451</t>
+          <t>1246589.84194932</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.409</t>
+          <t>820674.741120956</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.087</t>
+          <t>695906.346458109</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>1559341.17997004</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>1520128.67706356</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>1441826.50049391</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>1132162.57207338</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>1466404.64090303</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>1844653.63838054</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>1866917.92671887</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>1970229.13659699</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>2138233.46862849</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>1935662.09630991</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2041559.05520423</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>1942863.4094326</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.945</t>
+          <t>1562010.72597911</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>1054326.69161018</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>919394.310318241</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>148197.732393644</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>252.17</t>
+          <t>154555.396206786</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>249.89</t>
+          <t>168054.217503683</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>251.14</t>
+          <t>154804.50024608</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>264.75</t>
+          <t>166448.652207662</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>259.27</t>
+          <t>199000.056707812</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>245.57</t>
+          <t>174125.463571877</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>252.04</t>
+          <t>186166.474305133</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>262.97</t>
+          <t>223611.742831462</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>253.04</t>
+          <t>289120.505801717</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>253.6</t>
+          <t>327909.56113519</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>246.71</t>
+          <t>373577.44620443</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>239.09</t>
+          <t>436153.453196744</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>230.47</t>
+          <t>494948.776622255</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>223.91</t>
+          <t>407710.185299997</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>398.55</t>
+          <t>5597819699549.71</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>388.84</t>
+          <t>5407009199087.91</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>373.77</t>
+          <t>5820621517308.33</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>375.96</t>
+          <t>5706088658739.36</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>394.94</t>
+          <t>6501080654370.67</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>381.65</t>
+          <t>8844003148087.75</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>381.53</t>
+          <t>8764456549787.75</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>394.3</t>
+          <t>9000401153697.43</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>407.38</t>
+          <t>10248989741039.8</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>393.32</t>
+          <t>10851695822880.4</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>412.61</t>
+          <t>11177113913344.1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>403.15</t>
+          <t>10963907372579</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>392.4</t>
+          <t>9393879453627.65</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>380.63</t>
+          <t>7829268888090.54</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>370.89</t>
+          <t>6451971177571.4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>456.99</t>
+          <t>140581.430961096</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>456.33</t>
+          <t>157516.01026986</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>444.25</t>
+          <t>157672.57675118</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>456.64</t>
+          <t>106221.758194344</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>458.21</t>
+          <t>130177.744039377</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>452.05</t>
+          <t>173153.47173526</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>471.48</t>
+          <t>153240.259906808</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>489.7</t>
+          <t>164700.969649037</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>517.57</t>
+          <t>193962.743807858</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>511.43</t>
+          <t>240516.625421563</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>510.92</t>
+          <t>281709.808589289</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>499.25</t>
+          <t>331011.002020373</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>486.71</t>
+          <t>385382.978704207</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>472.78</t>
+          <t>473784.922435432</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>460.74</t>
+          <t>352512.873467787</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>31807441.389</t>
+          <t>4608774311962.93</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31674921.244</t>
+          <t>4589872856832.29</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>30568163.637</t>
+          <t>4628372321570.74</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>22550414.111</t>
+          <t>3477322988384.32</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>29734286.904</t>
+          <t>4609320738502.37</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>38988599.301</t>
+          <t>6834977951699.83</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40245149.746</t>
+          <t>6554405069616.21</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>43644515.834</t>
+          <t>6950720534748.87</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>47291309.626</t>
+          <t>7777461441672.52</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>43618209.678</t>
+          <t>7996502704746.53</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>46608793.23</t>
+          <t>8323176317558.86</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>44944259.25</t>
+          <t>8422072235523.23</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>36579167.181</t>
+          <t>7222134396208.5</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>24840875.383</t>
+          <t>6709894857894.87</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>21596521.507</t>
+          <t>4797804918133.93</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20035078.482</t>
+          <t>7616.30143254875</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19072042.144</t>
+          <t>-2960.61406307348</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17479043.687</t>
+          <t>10381.6407525029</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>12474509.107</t>
+          <t>48582.7420517361</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17036743.428</t>
+          <t>36270.9081682852</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>21610343.199</t>
+          <t>25846.5849725521</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21549294.307</t>
+          <t>20885.2036650692</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>23976495.678</t>
+          <t>21465.5046560963</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>26868724.541</t>
+          <t>29648.9990236033</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>24147804.672</t>
+          <t>48603.8803801539</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>25987288.093</t>
+          <t>46199.752545901</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>24757682.697</t>
+          <t>42566.4441840567</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>19908039.776</t>
+          <t>50770.4744925373</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>13186145.88</t>
+          <t>21163.8541868228</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>11147767.592</t>
+          <t>55197.31183221</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>37966219.052</t>
+          <t>989045387586.78</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>37504881.968</t>
+          <t>817136342255.629</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35712366.304</t>
+          <t>1192249195737.59</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>27143874.641</t>
+          <t>2228765670355.04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>35178333.384</t>
+          <t>1891759915868.3</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>46765126.614</t>
+          <t>2009025196387.92</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>47698517.4</t>
+          <t>2210051480171.54</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>51074387.566</t>
+          <t>2049680618948.56</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>55190632.172</t>
+          <t>2471528299367.24</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>52898856.214</t>
+          <t>2855193118133.82</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>57831830.219</t>
+          <t>2853937595785.21</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>56268820.023</t>
+          <t>2541835137055.74</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>46415659.254</t>
+          <t>2171745057419.15</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>34062035.169</t>
+          <t>1119374030195.67</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>29014081.647</t>
+          <t>1654166259437.47</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.707</t>
+          <t>274121.89465</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.894</t>
+          <t>287499.72846</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.765</t>
+          <t>268282.01642</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.218</t>
+          <t>180435.22768</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>227489.32958</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.724</t>
+          <t>259521.41133</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.663</t>
+          <t>240708.48946</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>270796.19484</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2.114</t>
+          <t>307219.55963</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2.435</t>
+          <t>357054.9163</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>416922.20117</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>3.364</t>
+          <t>466492.72549</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>515376.82677</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3.618</t>
+          <t>459994.19235</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>3.208</t>
+          <t>409732.13588</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19162007.8</t>
+          <t>-0.0311037571734734</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19053207.318</t>
+          <t>-0.0389042557898944</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18310944.931</t>
+          <t>-0.0322019601810935</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13238797.283</t>
+          <t>-0.0287825108329188</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17014851.168</t>
+          <t>-0.0205755306115161</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>22240873.779</t>
+          <t>-0.0190265316174358</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>23356270.816</t>
+          <t>-0.0188382346331709</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>25245019.15</t>
+          <t>-0.0125069685025224</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>27507082.559</t>
+          <t>-0.0126584369473392</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>25741233.882</t>
+          <t>-0.0040949701678003</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>27512872.614</t>
+          <t>-0.00512130265178204</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>26422867.459</t>
+          <t>-0.00412105377931646</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>21553148.532</t>
+          <t>0.00138864159816814</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>14530492.323</t>
+          <t>-0.0050566809743088</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>12699320.161</t>
+          <t>-0.00602637790458473</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>249110.987205519</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.962</t>
+          <t>272393.548705949</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>249618.697610976</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>161334.261309919</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>200645.101910896</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>229288.854944361</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>219964.217061377</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>250739.517668645</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>287975.197009048</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.185</t>
+          <t>322535.656092378</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.418</t>
+          <t>387647.803112496</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.579</t>
+          <t>440293.28298971</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.718</t>
+          <t>483677.734658298</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.543</t>
+          <t>439426.781156843</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.404</t>
+          <t>390590.697894541</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4469643.821</t>
+          <t>390388.35789602</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4384898.787</t>
+          <t>429108.845699053</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4125063.788</t>
+          <t>393881.896820065</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2959924.824</t>
+          <t>257613.676550789</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3919078.587</t>
+          <t>312348.682631458</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5070522.204</t>
+          <t>353831.571985482</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5196057.697</t>
+          <t>339803.996715696</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5700366.979</t>
+          <t>382243.187022735</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>6213786.874</t>
+          <t>433445.671955757</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5751229.076</t>
+          <t>475287.804818375</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>6147675.478</t>
+          <t>566607.454749689</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>5976420.092</t>
+          <t>633380.066717064</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4914959.557</t>
+          <t>684836.2921322</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3338471.861</t>
+          <t>619922.388725574</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2883069.577</t>
+          <t>550345.838391702</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>1760829.1189605</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>1877338.60876306</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>1815958.90185428</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>1339132.81334857</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>1562163.15089374</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>1701353.49363953</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>1594994.15101507</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>1798851.73688326</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>2103913.66621226</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>2357180.08736089</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>2795229.38105993</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>3142233.58718998</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>3440728.34002697</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>3360863.6263319</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>3066435.03210023</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1127.398</t>
+          <t>390388.35789602</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1049.835</t>
+          <t>428589.960716182</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1068.359</t>
+          <t>441970.169407685</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1174.662</t>
+          <t>408004.34827534</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1210.657</t>
+          <t>427374.866036795</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1407.2</t>
+          <t>459218.408752575</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1543.047</t>
+          <t>485951.913102854</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1480.086</t>
+          <t>510733.843279555</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1426.772</t>
+          <t>533263.829689562</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1156.414</t>
+          <t>544828.800386899</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1056.749</t>
+          <t>577464.20665302</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>902.779</t>
+          <t>605129.469906568</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>659.443</t>
+          <t>632759.282473243</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>482.767</t>
+          <t>654996.466782229</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>478.323</t>
+          <t>660805.520872823</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>249110.987205519</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>271693.846620992</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>277965.695940862</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>251566.758518966</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>274181.471253126</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>297858.188855432</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>314883.476316144</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>336240.636147866</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>357353.197563222</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>372975.201836446</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>397365.382260671</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>424694.737027864</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>448762.49721263</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>464523.411320782</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>468407.377087872</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>91114.8126439805</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>84984.9677209469</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>91659.1544999351</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>70390.3246992115</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>101118.468968542</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>120090.343264518</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>106259.381664304</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>128451.325217265</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>139604.580784243</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>170106.088941625</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>193764.353170311</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>222040.303592935</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>259928.2026578</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>230669.513284426</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>204113.781099333</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20035078481851.4</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>19072042144130.3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>17479043687391.6</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>12474509106876.1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>17036743427872</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>21610343199190.1</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>21549294307486.2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>23976495677623.6</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>26868724541010.9</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>24147804672358.3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>25987288093318.8</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>24757682697051.2</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>19908039775930.6</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>13186145879955.2</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>11147767592115.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>31807441389028.8</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>31674921243973.5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>30568163636971.4</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>22550414110557.5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>29734286903590.7</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>38988599300811.2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>40245149746278.7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>43644515833896.6</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>47291309625656.3</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>43618209678247.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>46608793230312.5</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>44944259250404.4</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>36579167180978.8</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>24840875383241.7</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>21596521507293.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>19162007799813.7</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>19053207317633.4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>18310944930775</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>13238797283045.2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>17014851168181</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>22240873778915.7</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>23356270815981.1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>25245019150008.3</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>27507082559422.2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>25741233882368.2</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>27512872614468.5</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>26422867459304.7</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>21553148531652.1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>14530492322654.8</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>12699320161235</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20398000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20837000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>21201000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>19918000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20277000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>21136000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>21557000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>22152000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>22117000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>22534000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>22830000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>23133000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>23418000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>23560890.1689708</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>23489944.7004608</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>12899000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>13200000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>13405000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>12296000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>12663000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>13361000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13659000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14182000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14403000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14894000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>15186000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>15551000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>15970000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>16067444.5297832</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>16019062.9800307</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>51162193207.3174</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>50854306766.5198</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>51302683701.8651</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>48438840955.0654</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>50338267495.631</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>51635804554.3794</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>52111252339.1222</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>53200369020.8505</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>53124251939.0588</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>55887330835.7667</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>54220886780.1216</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>54641265800.5858</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>53454995526.7301</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>53781163147.4982</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>53619219783.3406</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>32640760630.5048</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>32366566359.3398</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>32542481626.3838</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>29972519642.6025</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>31616610207.0647</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>32772416215.0786</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>33139630374.6316</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>34146108978.1279</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>34675124347.6904</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>37056547061.771</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>36350537931.0334</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>36940810197.7035</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>36652903972.2718</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>36876549870.3788</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>36765508899.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.331716691795572</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.354037887688592</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.360021341046824</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.385882898215127</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.39689266710716</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.399947745631216</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.427682288313345</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.457678077948967</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.463015386857404</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.469383418714181</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.490009375601123</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.436166942521148</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.430448852721004</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.435615610218396</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.42882899269932</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.419954649183771</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.427606828039</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.418059720586339</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.403877621841788</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.403828393058087</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.410036099509903</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.395258537696225</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.203544937111852</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.186941831018976</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.175791620163351</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.156716680514124</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.15458125513764</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.143873997758355</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.125686562528887</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.109872871637817</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.10458479151308</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0920090532044868</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0861606581312238</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.264457196852025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.279162503358605</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.289349291432411</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.313902096132527</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.325542157096532</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.32708265847282</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.342450577055497</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.372650802730414</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.379068724074233</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.385820132625152</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.398516741084111</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.468885762181886</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.46768117868951</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.470119431690414</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.465859789604328</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.459922710933326</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.467590107354008</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.467462732560993</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.456048864718562</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.455280579791477</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.462053049660315</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.459232263808909</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.23808561239466</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.224584889380456</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.211959848305746</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.191666685691717</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.185963703398713</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.176755805601743</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.161515261812081</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.142728903979596</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.137079267562861</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.123555389143104</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.113679566535551</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1108509.34671</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1192915.35281</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1131548.8462</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>789859.03294</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>995264.19459</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1154386.08155</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1074724.66787</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1220729.34865</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1373053.82031</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1590214.92382</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1913875.12857</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2184540.4385</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2450518.8305</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2409391.66177</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2086877.38964</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>481503.17054</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>514093.81342</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>485541.05132</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>328004.00125</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>413467.1516</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>473921.91525</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>446063.37838</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>510694.51224</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>573050.25274</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>645393.89376</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>760371.80792</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>855420.37031</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>944764.49479</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>850591.90201</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>754935.69005</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1354483967.86827</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1457969032.78694</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1552067726.24768</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1607502307.4535</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1670427170.49331</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1744651239.55253</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1816305945.149</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1895039613.93994</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1977196331.69843</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2058958231.97673</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2140992828.15616</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2225192944.02245</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2313261489.50933</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2392646349.28768</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2465814200.56571</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
